--- a/缓存数据/infoPlow_csm_8_Part.xlsx
+++ b/缓存数据/infoPlow_csm_8_Part.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>191.24</v>
+        <v>181.67</v>
       </c>
       <c r="C2" t="n">
-        <v>181.67</v>
+        <v>220.77</v>
       </c>
       <c r="D2" t="n">
-        <v>220.77</v>
+        <v>206.24</v>
       </c>
       <c r="E2" t="n">
-        <v>206.24</v>
+        <v>214.88</v>
       </c>
       <c r="F2" t="n">
-        <v>214.88</v>
+        <v>182.52</v>
       </c>
       <c r="G2" t="n">
-        <v>182.52</v>
+        <v>198.09</v>
       </c>
       <c r="H2" t="n">
-        <v>198.09</v>
+        <v>120.69</v>
       </c>
       <c r="I2" t="n">
-        <v>120.69</v>
+        <v>205.93</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>229.58</v>
+        <v>222.85</v>
       </c>
       <c r="C3" t="n">
-        <v>222.85</v>
+        <v>219.79</v>
       </c>
       <c r="D3" t="n">
-        <v>219.79</v>
+        <v>106.74</v>
       </c>
       <c r="E3" t="n">
-        <v>106.74</v>
+        <v>127.13</v>
       </c>
       <c r="F3" t="n">
-        <v>127.13</v>
+        <v>198.64</v>
       </c>
       <c r="G3" t="n">
-        <v>198.64</v>
+        <v>206.18</v>
       </c>
       <c r="H3" t="n">
-        <v>206.18</v>
+        <v>523.0099999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>523.01</v>
+        <v>627.1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123261.89</v>
+        <v>145381.08</v>
       </c>
       <c r="C4" t="n">
-        <v>145381.08</v>
+        <v>174865.67</v>
       </c>
       <c r="D4" t="n">
-        <v>174865.67</v>
+        <v>178841.83</v>
       </c>
       <c r="E4" t="n">
-        <v>178841.83</v>
+        <v>149009.1899999999</v>
       </c>
       <c r="F4" t="n">
-        <v>149009.19</v>
+        <v>140255.07</v>
       </c>
       <c r="G4" t="n">
-        <v>140255.0699999999</v>
+        <v>146435.3999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>146435.3999999999</v>
+        <v>157678.03</v>
       </c>
       <c r="I4" t="n">
-        <v>157678.0300000001</v>
+        <v>170260.72</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3899.059999999999</v>
+        <v>4100.76</v>
       </c>
       <c r="C5" t="n">
-        <v>4100.76</v>
+        <v>3997.59</v>
       </c>
       <c r="D5" t="n">
-        <v>3997.59</v>
+        <v>3879.98</v>
       </c>
       <c r="E5" t="n">
-        <v>3879.98</v>
+        <v>3829.01</v>
       </c>
       <c r="F5" t="n">
-        <v>3829.01</v>
+        <v>3767.54</v>
       </c>
       <c r="G5" t="n">
-        <v>3767.54</v>
+        <v>3738.17</v>
       </c>
       <c r="H5" t="n">
-        <v>3738.17</v>
+        <v>3842.47</v>
       </c>
       <c r="I5" t="n">
-        <v>3842.47</v>
+        <v>2490.02</v>
       </c>
     </row>
     <row r="6">
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>794.88</v>
+        <v>788.5800000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>788.5800000000002</v>
+        <v>778.3099999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>778.3099999999999</v>
+        <v>817.6600000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>817.6600000000001</v>
+        <v>788.35</v>
       </c>
       <c r="F8" t="n">
-        <v>788.35</v>
+        <v>790</v>
       </c>
       <c r="G8" t="n">
-        <v>790</v>
+        <v>784.2399999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>784.2399999999999</v>
+        <v>764.29</v>
       </c>
       <c r="I8" t="n">
-        <v>764.29</v>
+        <v>680.0799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>325059.7100000003</v>
+        <v>324895.5699999999</v>
       </c>
       <c r="C9" t="n">
-        <v>324895.5699999999</v>
+        <v>361294.62</v>
       </c>
       <c r="D9" t="n">
-        <v>361294.62</v>
+        <v>372461.6499999998</v>
       </c>
       <c r="E9" t="n">
-        <v>372461.6499999998</v>
+        <v>332628.0399999999</v>
       </c>
       <c r="F9" t="n">
-        <v>332628.0399999999</v>
+        <v>311344.2099999999</v>
       </c>
       <c r="G9" t="n">
-        <v>311344.21</v>
+        <v>335440.7800000001</v>
       </c>
       <c r="H9" t="n">
-        <v>335440.7800000001</v>
+        <v>376177.4500000007</v>
       </c>
       <c r="I9" t="n">
-        <v>376177.4500000005</v>
+        <v>407522.0399999998</v>
       </c>
     </row>
     <row r="10">
@@ -730,28 +730,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207.56</v>
+        <v>311.64</v>
       </c>
       <c r="C10" t="n">
-        <v>311.64</v>
+        <v>887.92</v>
       </c>
       <c r="D10" t="n">
-        <v>887.92</v>
+        <v>791.6799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>791.6800000000001</v>
+        <v>399.09</v>
       </c>
       <c r="F10" t="n">
-        <v>399.09</v>
+        <v>718.95</v>
       </c>
       <c r="G10" t="n">
-        <v>718.95</v>
+        <v>223.49</v>
       </c>
       <c r="H10" t="n">
-        <v>223.49</v>
+        <v>236.39</v>
       </c>
       <c r="I10" t="n">
-        <v>236.39</v>
+        <v>263.87</v>
       </c>
     </row>
     <row r="11">
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8698.420000000002</v>
+        <v>8602.709999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>8602.709999999999</v>
+        <v>7756.18</v>
       </c>
       <c r="D11" t="n">
-        <v>7756.179999999999</v>
+        <v>8445.170000000004</v>
       </c>
       <c r="E11" t="n">
-        <v>8445.170000000002</v>
+        <v>10326.63</v>
       </c>
       <c r="F11" t="n">
-        <v>10326.63</v>
+        <v>9599.85</v>
       </c>
       <c r="G11" t="n">
-        <v>9599.85</v>
+        <v>8183.110000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>8183.110000000001</v>
+        <v>8253.16</v>
       </c>
       <c r="I11" t="n">
-        <v>8253.16</v>
+        <v>9046.110000000002</v>
       </c>
     </row>
     <row r="12">
@@ -792,28 +792,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20173.51</v>
+        <v>20625.66</v>
       </c>
       <c r="C12" t="n">
-        <v>20625.66</v>
+        <v>19969.58</v>
       </c>
       <c r="D12" t="n">
-        <v>19969.58</v>
+        <v>19103.22</v>
       </c>
       <c r="E12" t="n">
-        <v>19103.22</v>
+        <v>19885.78</v>
       </c>
       <c r="F12" t="n">
-        <v>19885.78</v>
+        <v>16342.55</v>
       </c>
       <c r="G12" t="n">
-        <v>16342.55</v>
+        <v>15226.17</v>
       </c>
       <c r="H12" t="n">
-        <v>15226.17</v>
+        <v>18883.94</v>
       </c>
       <c r="I12" t="n">
-        <v>18883.94</v>
+        <v>17261.74</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/infoPlow_csm_8_Part.xlsx
+++ b/缓存数据/infoPlow_csm_8_Part.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>181.67</v>
+        <v>548.4400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>220.77</v>
+        <v>1244.59</v>
       </c>
       <c r="D2" t="n">
-        <v>206.24</v>
+        <v>1533.7</v>
       </c>
       <c r="E2" t="n">
-        <v>214.88</v>
+        <v>986.8399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>182.52</v>
+        <v>785.3799999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>198.09</v>
+        <v>759.76</v>
       </c>
       <c r="H2" t="n">
-        <v>120.69</v>
+        <v>804.4400000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>205.93</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>222.85</v>
+        <v>163.02</v>
       </c>
       <c r="C3" t="n">
-        <v>219.79</v>
+        <v>759.03</v>
       </c>
       <c r="D3" t="n">
-        <v>106.74</v>
+        <v>160.66</v>
       </c>
       <c r="E3" t="n">
-        <v>127.13</v>
+        <v>156.8</v>
       </c>
       <c r="F3" t="n">
-        <v>198.64</v>
+        <v>147.4</v>
       </c>
       <c r="G3" t="n">
-        <v>206.18</v>
+        <v>178.84</v>
       </c>
       <c r="H3" t="n">
-        <v>523.0099999999999</v>
+        <v>179.93</v>
       </c>
       <c r="I3" t="n">
-        <v>627.1</v>
+        <v>210.71</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145381.08</v>
+        <v>211918.77</v>
       </c>
       <c r="C4" t="n">
-        <v>174865.67</v>
+        <v>183090.62</v>
       </c>
       <c r="D4" t="n">
-        <v>178841.83</v>
+        <v>155508.58</v>
       </c>
       <c r="E4" t="n">
-        <v>149009.1899999999</v>
+        <v>200015.83</v>
       </c>
       <c r="F4" t="n">
-        <v>140255.07</v>
+        <v>248853.94</v>
       </c>
       <c r="G4" t="n">
-        <v>146435.3999999999</v>
+        <v>193583.72</v>
       </c>
       <c r="H4" t="n">
-        <v>157678.03</v>
+        <v>191486.43</v>
       </c>
       <c r="I4" t="n">
-        <v>170260.72</v>
+        <v>164635.36</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4100.76</v>
+        <v>862.28</v>
       </c>
       <c r="C5" t="n">
-        <v>3997.59</v>
+        <v>2076.76</v>
       </c>
       <c r="D5" t="n">
-        <v>3879.98</v>
+        <v>1799.43</v>
       </c>
       <c r="E5" t="n">
-        <v>3829.01</v>
+        <v>2756.15</v>
       </c>
       <c r="F5" t="n">
-        <v>3767.54</v>
+        <v>2689.47</v>
       </c>
       <c r="G5" t="n">
-        <v>3738.17</v>
+        <v>1456.33</v>
       </c>
       <c r="H5" t="n">
-        <v>3842.47</v>
+        <v>2097.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2490.02</v>
+        <v>3136.11</v>
       </c>
     </row>
     <row r="6">
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>788.5800000000002</v>
+        <v>375.61</v>
       </c>
       <c r="C8" t="n">
-        <v>778.3099999999999</v>
+        <v>340.86</v>
       </c>
       <c r="D8" t="n">
-        <v>817.6600000000001</v>
+        <v>603.3100000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>788.35</v>
+        <v>782.7900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>790</v>
+        <v>749.2900000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>784.2399999999999</v>
+        <v>747.01</v>
       </c>
       <c r="H8" t="n">
-        <v>764.29</v>
+        <v>746.8099999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>680.0799999999999</v>
+        <v>746.78</v>
       </c>
     </row>
     <row r="9">
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>324895.5699999999</v>
+        <v>223773.99</v>
       </c>
       <c r="C9" t="n">
-        <v>361294.62</v>
+        <v>216338.59</v>
       </c>
       <c r="D9" t="n">
-        <v>372461.6499999998</v>
+        <v>194591.0500000001</v>
       </c>
       <c r="E9" t="n">
-        <v>332628.0399999999</v>
+        <v>213596.4699999999</v>
       </c>
       <c r="F9" t="n">
-        <v>311344.2099999999</v>
+        <v>209518.89</v>
       </c>
       <c r="G9" t="n">
-        <v>335440.7800000001</v>
+        <v>193661.6699999999</v>
       </c>
       <c r="H9" t="n">
-        <v>376177.4500000007</v>
+        <v>175431.2800000002</v>
       </c>
       <c r="I9" t="n">
-        <v>407522.0399999998</v>
+        <v>167602.8299999999</v>
       </c>
     </row>
     <row r="10">
@@ -730,28 +730,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>311.64</v>
+        <v>1795.03</v>
       </c>
       <c r="C10" t="n">
-        <v>887.92</v>
+        <v>2585.52</v>
       </c>
       <c r="D10" t="n">
-        <v>791.6799999999999</v>
+        <v>2726.35</v>
       </c>
       <c r="E10" t="n">
-        <v>399.09</v>
+        <v>148.02</v>
       </c>
       <c r="F10" t="n">
-        <v>718.95</v>
+        <v>80.7</v>
       </c>
       <c r="G10" t="n">
-        <v>223.49</v>
+        <v>170.43</v>
       </c>
       <c r="H10" t="n">
-        <v>236.39</v>
+        <v>196.78</v>
       </c>
       <c r="I10" t="n">
-        <v>263.87</v>
+        <v>202.66</v>
       </c>
     </row>
     <row r="11">
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8602.709999999999</v>
+        <v>4300.98</v>
       </c>
       <c r="C11" t="n">
-        <v>7756.18</v>
+        <v>3251.719999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>8445.170000000004</v>
+        <v>4262.070000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>10326.63</v>
+        <v>5048.469999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>9599.85</v>
+        <v>2766.56</v>
       </c>
       <c r="G11" t="n">
-        <v>8183.110000000001</v>
+        <v>1763.99</v>
       </c>
       <c r="H11" t="n">
-        <v>8253.16</v>
+        <v>3105.760000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>9046.110000000002</v>
+        <v>4381.35</v>
       </c>
     </row>
     <row r="12">
@@ -792,31 +792,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20625.66</v>
+        <v>18090.08</v>
       </c>
       <c r="C12" t="n">
-        <v>19969.58</v>
+        <v>15250.92</v>
       </c>
       <c r="D12" t="n">
-        <v>19103.22</v>
+        <v>14310.16</v>
       </c>
       <c r="E12" t="n">
-        <v>19885.78</v>
+        <v>16776.97</v>
       </c>
       <c r="F12" t="n">
-        <v>16342.55</v>
+        <v>17032.77</v>
       </c>
       <c r="G12" t="n">
-        <v>15226.17</v>
+        <v>17023.47</v>
       </c>
       <c r="H12" t="n">
-        <v>18883.94</v>
+        <v>17612.77</v>
       </c>
       <c r="I12" t="n">
-        <v>17261.74</v>
+        <v>14439.45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>